--- a/public/downloads/snag-list-template.xlsx
+++ b/public/downloads/snag-list-template.xlsx
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B14" s="28"/>
       <x:c r="C14" s="25" t="str">
-        <x:v>https://snaglist.dev/snag-list-template</x:v>
+        <x:v>https://usesnaglist.com/snag-list-template</x:v>
       </x:c>
       <x:c r="D14" s="25"/>
       <x:c r="E14" s="25"/>
